--- a/Minimal_zaxir_3oylik/Min_Zaxira.xlsx
+++ b/Minimal_zaxir_3oylik/Min_Zaxira.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_HP\Desktop\NEJAVIYKA\Minimal_zaxir_3oylik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F8F0EB-DD04-4472-A1BA-B38A3AF3AD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44595155-D83C-4E2B-8813-761D437165C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="708" yWindow="612" windowWidth="21552" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1488" yWindow="1320" windowWidth="21552" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Min_Zaxira" sheetId="1" r:id="rId1"/>
@@ -5428,7 +5428,7 @@
         <v>132</v>
       </c>
       <c r="F39">
-        <v>8950</v>
+        <v>500</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -5928,7 +5928,7 @@
         <v>0.77</v>
       </c>
       <c r="F64">
-        <v>100</v>
+        <v>800</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -6108,7 +6108,7 @@
         <v>0.51800000000000002</v>
       </c>
       <c r="F73">
-        <v>50</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -20988,7 +20988,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="F817">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.3">
@@ -21088,7 +21088,7 @@
         <v>33</v>
       </c>
       <c r="F822">
-        <v>2250</v>
+        <v>600</v>
       </c>
     </row>
     <row r="823" spans="1:6" x14ac:dyDescent="0.3">
@@ -21428,7 +21428,7 @@
         <v>0.52600000000000002</v>
       </c>
       <c r="F839">
-        <v>50</v>
+        <v>200</v>
       </c>
     </row>
     <row r="840" spans="1:6" x14ac:dyDescent="0.3">
@@ -21828,7 +21828,7 @@
         <v>12.792</v>
       </c>
       <c r="F859">
-        <v>4000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.3">
@@ -21988,7 +21988,7 @@
         <v>3.6030000000000002</v>
       </c>
       <c r="F867">
-        <v>250</v>
+        <v>900</v>
       </c>
     </row>
     <row r="868" spans="1:6" x14ac:dyDescent="0.3">
@@ -22348,7 +22348,7 @@
         <v>11.465999999999999</v>
       </c>
       <c r="F885">
-        <v>3000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="886" spans="1:6" x14ac:dyDescent="0.3">
@@ -22968,7 +22968,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="F916">
-        <v>1000</v>
+        <v>400</v>
       </c>
     </row>
     <row r="917" spans="1:6" x14ac:dyDescent="0.3">
@@ -28228,7 +28228,7 @@
         <v>1.619</v>
       </c>
       <c r="F1179">
-        <v>6500</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="1180" spans="1:6" x14ac:dyDescent="0.3">
